--- a/artfynd/A 53842-2025 artfynd.xlsx
+++ b/artfynd/A 53842-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>7120922</v>
+        <v>7126716</v>
       </c>
       <c r="B2" t="n">
-        <v>93132</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96437</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2671</v>
+        <v>2667</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>565289.807840794</v>
+        <v>565290</v>
       </c>
       <c r="R2" t="n">
-        <v>6437699.058764022</v>
+        <v>6437699</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -752,24 +747,14 @@
           <t>2011-11-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2011-11-01</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Sveaskogs Naturvärdesinventering -Inventerare: Mille Fagerström  ID;32786</t>
+          <t>Sveaskogs Naturvärdesinventering -Inventerare: Mille Fagerström  ID;32787</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,15 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>7120233</v>
+        <v>7120922</v>
       </c>
       <c r="B3" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,26 +792,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>2671</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -840,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>565289.807840794</v>
+        <v>565290</v>
       </c>
       <c r="R3" t="n">
-        <v>6437699.058764022</v>
+        <v>6437699</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -873,24 +853,14 @@
           <t>2011-11-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2011-11-01</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Sveaskogs Naturvärdesinventering -Inventerare: Mille Fagerström  ID;32785</t>
+          <t>Sveaskogs Naturvärdesinventering -Inventerare: Mille Fagerström  ID;32786</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,57 +887,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>7126716</v>
+        <v>74569883</v>
       </c>
       <c r="B4" t="n">
-        <v>93145</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102240</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2667</v>
+        <v>221235</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neckera complanata</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Huebener</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Mosshult, Sm</t>
+          <t>Domra 600 m V, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>565289.807840794</v>
+        <v>565433</v>
       </c>
       <c r="R4" t="n">
-        <v>6437699.058764022</v>
+        <v>6437803</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -991,27 +952,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2011-11-01</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1983-01-01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2011-11-01</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1987-12-31</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Sveaskogs Naturvärdesinventering -Inventerare: Mille Fagerström  ID;32787</t>
+          <t>Smålands flora 2007: KOO: 7G7d 4229. SOM: Lathyrus vernus. LEG: Ingemar Hultgren</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,22 +977,26 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Sveaskog genom Johan Ekenstedt</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Sveaskog genom Johan Ekenstedt</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Via Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Smålands flora (1978-2007)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>74569883</v>
+        <v>7120233</v>
       </c>
       <c r="B5" t="n">
-        <v>101762</v>
+        <v>101326</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1049,37 +1004,41 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221235</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Domra 600 m V, Sm</t>
+          <t>Mosshult, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>565433</v>
+        <v>565290</v>
       </c>
       <c r="R5" t="n">
-        <v>6437803</v>
+        <v>6437699</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1103,17 +1062,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>1983-01-01</t>
+          <t>2011-11-01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1987-12-31</t>
+          <t>2011-11-01</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 7G7d 4229. SOM: Lathyrus vernus. LEG: Ingemar Hultgren</t>
+          <t>Sveaskogs Naturvärdesinventering -Inventerare: Mille Fagerström  ID;32785</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,19 +1087,15 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Sveaskog genom Johan Ekenstedt</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Via Margareta Edqvist</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Smålands flora (1978-2007)</t>
-        </is>
-      </c>
+          <t>Sveaskog genom Johan Ekenstedt</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
